--- a/artfynd/A 34913-2025 artfynd.xlsx
+++ b/artfynd/A 34913-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY10"/>
+  <dimension ref="A1:AY21"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,56 +675,44 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>7262071</v>
+        <v>179294</v>
       </c>
       <c r="B2" t="n">
-        <v>98520</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>108063</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>222498</v>
+        <v>286</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Finnklint</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
-        </is>
-      </c>
-      <c r="H2" t="inlineStr">
-        <is>
-          <t>Schreb.</t>
-        </is>
-      </c>
+          <t>Centaurea phrygia subsp. phrygia</t>
+        </is>
+      </c>
+      <c r="H2" t="inlineStr"/>
       <c r="I2" t="inlineStr"/>
-      <c r="J2" t="inlineStr"/>
-      <c r="K2" t="inlineStr"/>
-      <c r="L2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
-          <t>Saxberget, Dlr</t>
+          <t>Saxbergets östra sida, Dlr</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>499163.4192160164</v>
+        <v>499178</v>
       </c>
       <c r="R2" t="n">
-        <v>6666234.013686877</v>
+        <v>6666224</v>
       </c>
       <c r="S2" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -746,24 +734,24 @@
           <t>Grangärde</t>
         </is>
       </c>
+      <c r="X2" t="inlineStr">
+        <is>
+          <t>W-Lud-0008</t>
+        </is>
+      </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>2014-04-18</t>
-        </is>
-      </c>
-      <c r="Z2" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>1996-08-12</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>2014-04-18</t>
-        </is>
-      </c>
-      <c r="AB2" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>1996-08-12</t>
+        </is>
+      </c>
+      <c r="AC2" t="inlineStr">
+        <is>
+          <t>inom 25 m2 (Katrine Svensson)</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -775,89 +763,69 @@
       <c r="AG2" t="b">
         <v>0</v>
       </c>
-      <c r="AH2" t="inlineStr">
-        <is>
-          <t>Barrskog i branter</t>
-        </is>
-      </c>
       <c r="AI2" t="inlineStr">
         <is>
-          <t>lövrikt</t>
+          <t>bland piprör på nyupptaget hygge</t>
         </is>
       </c>
       <c r="AT2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>Janolof Hermansson</t>
+          <t>Dalarna Floraväktarna</t>
         </is>
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>Janolof Hermansson</t>
-        </is>
-      </c>
-      <c r="AY2" t="inlineStr"/>
+          <t>Via Dalarna Floraväktarna</t>
+        </is>
+      </c>
+      <c r="AY2" t="inlineStr">
+        <is>
+          <t>Floraväkteri Sverige</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>7262075</v>
+        <v>132256</v>
       </c>
       <c r="B3" t="n">
-        <v>78569</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80305</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>6458</v>
+        <v>392</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Aspgelélav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Collema subnigrescens</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
-        </is>
-      </c>
-      <c r="I3" t="inlineStr">
-        <is>
-          <t>12</t>
-        </is>
-      </c>
-      <c r="J3" t="inlineStr">
-        <is>
-          <t>dm²</t>
-        </is>
-      </c>
-      <c r="K3" t="inlineStr">
-        <is>
-          <t>med apothecier</t>
-        </is>
-      </c>
+          <t>Degel.</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Saxberget, Dlr</t>
+          <t>Saxberget, nordostsluttning, Dlr</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>499112.5287470957</v>
+        <v>499188</v>
       </c>
       <c r="R3" t="n">
-        <v>6666284.34478725</v>
+        <v>6666322</v>
       </c>
       <c r="S3" t="n">
         <v>5</v>
@@ -884,27 +852,17 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>2014-04-18</t>
-        </is>
-      </c>
-      <c r="Z3" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2010-11-08</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>2014-04-18</t>
-        </is>
-      </c>
-      <c r="AB3" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2010-11-08</t>
         </is>
       </c>
       <c r="AC3" t="inlineStr">
         <is>
-          <t>Laven ser mycket frisk ut och det finns många små bålar mellan de större.</t>
+          <t>Skogen avverkad för ca 15 år sedan och många grova aspar lämnades. Idag 5-10 m hög granskog.</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -918,32 +876,15 @@
       </c>
       <c r="AI3" t="inlineStr">
         <is>
-          <t>lövrikt</t>
-        </is>
-      </c>
-      <c r="AJ3" t="inlineStr">
-        <is>
-          <t>asp</t>
-        </is>
-      </c>
-      <c r="AK3" t="inlineStr">
-        <is>
-          <t>Populus tremula</t>
-        </is>
-      </c>
-      <c r="AL3" t="inlineStr">
-        <is>
-          <t>gammalt klent träd</t>
-        </is>
-      </c>
-      <c r="AM3" t="inlineStr">
-        <is>
-          <t>Bark på levande träd</t>
-        </is>
+          <t>grov asp i ung granskog</t>
+        </is>
+      </c>
+      <c r="AN3" t="n">
+        <v>1</v>
       </c>
       <c r="AO3" t="inlineStr">
         <is>
-          <t>Bark on living woody plant # Populus tremula # gammalt klent träd</t>
+          <t>1 substratenheter</t>
         </is>
       </c>
       <c r="AT3" t="inlineStr"/>
@@ -961,67 +902,51 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>7262079</v>
+        <v>118767476</v>
       </c>
       <c r="B4" t="n">
-        <v>78569</v>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91966</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>6458</v>
+        <v>5321</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Barkticka</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Oxyporus corticola</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
-        </is>
-      </c>
-      <c r="I4" t="inlineStr">
-        <is>
-          <t>60</t>
-        </is>
-      </c>
-      <c r="J4" t="inlineStr">
-        <is>
-          <t>dm²</t>
-        </is>
-      </c>
-      <c r="K4" t="inlineStr">
-        <is>
-          <t>med apothecier</t>
-        </is>
-      </c>
+          <t>(Fr.) Ryvarden</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr"/>
+      <c r="J4" t="inlineStr"/>
+      <c r="K4" t="inlineStr"/>
+      <c r="N4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
-          <t>Saxberget, Dlr</t>
+          <t>Saxbergets östra sida,, Saxberget, Björnhyttan, Dlr</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>499146.4685857474</v>
+        <v>499200</v>
       </c>
       <c r="R4" t="n">
-        <v>6666306.755938976</v>
+        <v>6666216</v>
       </c>
       <c r="S4" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -1045,22 +970,12 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>2014-04-18</t>
-        </is>
-      </c>
-      <c r="Z4" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2024-07-29</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>2014-04-18</t>
-        </is>
-      </c>
-      <c r="AB4" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2024-07-29</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1069,58 +984,29 @@
       <c r="AE4" t="b">
         <v>0</v>
       </c>
+      <c r="AF4" t="inlineStr"/>
       <c r="AG4" t="b">
         <v>0</v>
-      </c>
-      <c r="AI4" t="inlineStr">
-        <is>
-          <t>lövrikt</t>
-        </is>
-      </c>
-      <c r="AJ4" t="inlineStr">
-        <is>
-          <t>asp</t>
-        </is>
-      </c>
-      <c r="AK4" t="inlineStr">
-        <is>
-          <t>Populus tremula</t>
-        </is>
-      </c>
-      <c r="AL4" t="inlineStr">
-        <is>
-          <t>klent träd</t>
-        </is>
-      </c>
-      <c r="AO4" t="inlineStr">
-        <is>
-          <t>Populus tremula # klent träd</t>
-        </is>
       </c>
       <c r="AT4" t="inlineStr"/>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>Janolof Hermansson</t>
+          <t>Alec Bailey</t>
         </is>
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>Janolof Hermansson</t>
+          <t>Alec Bailey</t>
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>95038138</v>
+        <v>118767672</v>
       </c>
       <c r="B5" t="n">
-        <v>57150</v>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91966</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1128,58 +1014,40 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>208260</v>
+        <v>5321</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Huggorm</t>
+          <t>Barkticka</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Vipera berus</t>
+          <t>Oxyporus corticola</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I5" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J5" t="inlineStr">
-        <is>
-          <t>ex.</t>
-        </is>
-      </c>
+          <t>(Fr.) Ryvarden</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr"/>
+      <c r="J5" t="inlineStr"/>
       <c r="K5" t="inlineStr"/>
-      <c r="L5" t="inlineStr"/>
-      <c r="M5" t="inlineStr">
-        <is>
-          <t>vilande</t>
-        </is>
-      </c>
-      <c r="N5" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
+      <c r="N5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
-          <t>Saxberget, Dlr</t>
+          <t>Saxbergets östra sida, Saxberget, Björnhyttan, Dlr</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>499270.6737968944</v>
+        <v>499141</v>
       </c>
       <c r="R5" t="n">
-        <v>6666031.710861046</v>
+        <v>6666238</v>
       </c>
       <c r="S5" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
@@ -1203,27 +1071,12 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>2021-06-29</t>
-        </is>
-      </c>
-      <c r="Z5" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2024-07-29</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>2021-06-29</t>
-        </is>
-      </c>
-      <c r="AB5" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
-      <c r="AC5" t="inlineStr">
-        <is>
-          <t>Vilande på stig</t>
+          <t>2024-07-29</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1236,35 +1089,25 @@
       <c r="AG5" t="b">
         <v>0</v>
       </c>
-      <c r="AI5" t="inlineStr">
-        <is>
-          <t>Skogsmark</t>
-        </is>
-      </c>
       <c r="AT5" t="inlineStr"/>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>Henrik Larsson</t>
+          <t>Alec Bailey</t>
         </is>
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>Henrik Larsson</t>
+          <t>Alec Bailey</t>
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>95038065</v>
+        <v>7262074</v>
       </c>
       <c r="B6" t="n">
-        <v>78569</v>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80432</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1289,23 +1132,30 @@
           <t>(L.) Hoffm.</t>
         </is>
       </c>
-      <c r="I6" t="inlineStr"/>
-      <c r="J6" t="inlineStr"/>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="J6" t="inlineStr">
+        <is>
+          <t>dm²</t>
+        </is>
+      </c>
       <c r="K6" t="inlineStr"/>
-      <c r="N6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
           <t>Saxberget, Dlr</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>499156.4346407815</v>
+        <v>499105</v>
       </c>
       <c r="R6" t="n">
-        <v>6666242.983104819</v>
+        <v>6666291</v>
       </c>
       <c r="S6" t="n">
-        <v>25</v>
+        <v>5</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
@@ -1329,27 +1179,12 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>2021-06-23</t>
-        </is>
-      </c>
-      <c r="Z6" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2014-04-18</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
         <is>
-          <t>2021-06-23</t>
-        </is>
-      </c>
-      <c r="AB6" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
-      <c r="AC6" t="inlineStr">
-        <is>
-          <t>På två lövträd</t>
+          <t>2014-04-18</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1358,44 +1193,58 @@
       <c r="AE6" t="b">
         <v>0</v>
       </c>
-      <c r="AF6" t="inlineStr"/>
       <c r="AG6" t="b">
         <v>0</v>
       </c>
       <c r="AI6" t="inlineStr">
         <is>
-          <t>Skogsmark</t>
+          <t>lövrikt</t>
+        </is>
+      </c>
+      <c r="AJ6" t="inlineStr">
+        <is>
+          <t>asp</t>
+        </is>
+      </c>
+      <c r="AK6" t="inlineStr">
+        <is>
+          <t>Populus tremula</t>
+        </is>
+      </c>
+      <c r="AL6" t="inlineStr">
+        <is>
+          <t>gammalt träd</t>
+        </is>
+      </c>
+      <c r="AM6" t="inlineStr">
+        <is>
+          <t>Bark på dött träd</t>
         </is>
       </c>
       <c r="AO6" t="inlineStr">
         <is>
-          <t>På två lövträd</t>
+          <t>Bark of dead wood # avbruten topp på marken # Populus tremula # gammalt träd</t>
         </is>
       </c>
       <c r="AT6" t="inlineStr"/>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>Henrik Larsson</t>
+          <t>Janolof Hermansson</t>
         </is>
       </c>
       <c r="AX6" t="inlineStr">
         <is>
-          <t>Henrik Larsson</t>
+          <t>Janolof Hermansson</t>
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>103879479</v>
+        <v>7262075</v>
       </c>
       <c r="B7" t="n">
-        <v>4941</v>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80432</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1403,50 +1252,51 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>105212</v>
+        <v>6458</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Barrpraktbagge</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Chrysobothris chrysostigma</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>6</t>
-        </is>
-      </c>
-      <c r="J7" t="inlineStr"/>
-      <c r="K7" t="inlineStr"/>
-      <c r="L7" t="inlineStr"/>
-      <c r="M7" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
-      <c r="N7" t="inlineStr"/>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="J7" t="inlineStr">
+        <is>
+          <t>dm²</t>
+        </is>
+      </c>
+      <c r="K7" t="inlineStr">
+        <is>
+          <t>med apothecier</t>
+        </is>
+      </c>
       <c r="P7" t="inlineStr">
         <is>
-          <t>Saxdals leden, Saxberget, Björnhyttan, Dlr</t>
+          <t>Saxberget, Dlr</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>499025.100133114</v>
+        <v>499113</v>
       </c>
       <c r="R7" t="n">
-        <v>6665919.662124671</v>
+        <v>6666284</v>
       </c>
       <c r="S7" t="n">
-        <v>25</v>
+        <v>5</v>
       </c>
       <c r="T7" t="inlineStr">
         <is>
@@ -1470,27 +1320,17 @@
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>2022-10-02</t>
-        </is>
-      </c>
-      <c r="Z7" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2014-04-18</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
         <is>
-          <t>2022-10-02</t>
-        </is>
-      </c>
-      <c r="AB7" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2014-04-18</t>
         </is>
       </c>
       <c r="AC7" t="inlineStr">
         <is>
-          <t>Gnagspåren kan vara mellan 2 och 5 år gamla</t>
+          <t>Laven ser mycket frisk ut och det finns många små bålar mellan de större.</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1499,75 +1339,106 @@
       <c r="AE7" t="b">
         <v>0</v>
       </c>
-      <c r="AF7" t="inlineStr"/>
       <c r="AG7" t="b">
         <v>0</v>
+      </c>
+      <c r="AI7" t="inlineStr">
+        <is>
+          <t>lövrikt</t>
+        </is>
+      </c>
+      <c r="AJ7" t="inlineStr">
+        <is>
+          <t>asp</t>
+        </is>
+      </c>
+      <c r="AK7" t="inlineStr">
+        <is>
+          <t>Populus tremula</t>
+        </is>
+      </c>
+      <c r="AL7" t="inlineStr">
+        <is>
+          <t>gammalt klent träd</t>
+        </is>
+      </c>
+      <c r="AM7" t="inlineStr">
+        <is>
+          <t>Bark på levande träd</t>
+        </is>
+      </c>
+      <c r="AO7" t="inlineStr">
+        <is>
+          <t>Bark on living woody plant # Populus tremula # gammalt klent träd</t>
+        </is>
       </c>
       <c r="AT7" t="inlineStr"/>
       <c r="AW7" t="inlineStr">
         <is>
-          <t>Alec Bailey</t>
+          <t>Janolof Hermansson</t>
         </is>
       </c>
       <c r="AX7" t="inlineStr">
         <is>
-          <t>Alec Bailey</t>
+          <t>Janolof Hermansson</t>
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>118767672</v>
+        <v>7262076</v>
       </c>
       <c r="B8" t="n">
-        <v>90922</v>
-      </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80432</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>5321</v>
+        <v>6458</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Barkticka</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Rigidoporus corticola</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Fr.) Pouzar</t>
-        </is>
-      </c>
-      <c r="I8" t="inlineStr"/>
-      <c r="J8" t="inlineStr"/>
+          <t>(L.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="J8" t="inlineStr">
+        <is>
+          <t>dm²</t>
+        </is>
+      </c>
       <c r="K8" t="inlineStr"/>
-      <c r="N8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
-          <t>Saxbergets östra sida, Saxberget, Björnhyttan, Dlr</t>
+          <t>Saxberget, Dlr</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>499141</v>
+        <v>499124</v>
       </c>
       <c r="R8" t="n">
-        <v>6666238</v>
+        <v>6666324</v>
       </c>
       <c r="S8" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T8" t="inlineStr">
         <is>
@@ -1591,12 +1462,12 @@
       </c>
       <c r="Y8" t="inlineStr">
         <is>
-          <t>2024-07-29</t>
+          <t>2014-04-18</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
         <is>
-          <t>2024-07-29</t>
+          <t>2014-04-18</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1605,34 +1476,58 @@
       <c r="AE8" t="b">
         <v>0</v>
       </c>
-      <c r="AF8" t="inlineStr"/>
       <c r="AG8" t="b">
         <v>0</v>
+      </c>
+      <c r="AI8" t="inlineStr">
+        <is>
+          <t>lövrikt, men i lucka efter avverkning för länge sedan</t>
+        </is>
+      </c>
+      <c r="AJ8" t="inlineStr">
+        <is>
+          <t>rönn</t>
+        </is>
+      </c>
+      <c r="AK8" t="inlineStr">
+        <is>
+          <t>Sorbus aucuparia</t>
+        </is>
+      </c>
+      <c r="AL8" t="inlineStr">
+        <is>
+          <t>gammalt klent träd</t>
+        </is>
+      </c>
+      <c r="AM8" t="inlineStr">
+        <is>
+          <t>Bark på levande träd</t>
+        </is>
+      </c>
+      <c r="AO8" t="inlineStr">
+        <is>
+          <t>Bark on living woody plant # Sorbus aucuparia # gammalt klent träd</t>
+        </is>
       </c>
       <c r="AT8" t="inlineStr"/>
       <c r="AW8" t="inlineStr">
         <is>
-          <t>Alec Bailey</t>
+          <t>Janolof Hermansson</t>
         </is>
       </c>
       <c r="AX8" t="inlineStr">
         <is>
-          <t>Alec Bailey</t>
+          <t>Janolof Hermansson</t>
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>118767473</v>
+        <v>7262079</v>
       </c>
       <c r="B9" t="n">
-        <v>79574</v>
-      </c>
-      <c r="C9" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80432</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1657,23 +1552,34 @@
           <t>(L.) Hoffm.</t>
         </is>
       </c>
-      <c r="I9" t="inlineStr"/>
-      <c r="J9" t="inlineStr"/>
-      <c r="K9" t="inlineStr"/>
-      <c r="N9" t="inlineStr"/>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>60</t>
+        </is>
+      </c>
+      <c r="J9" t="inlineStr">
+        <is>
+          <t>dm²</t>
+        </is>
+      </c>
+      <c r="K9" t="inlineStr">
+        <is>
+          <t>med apothecier</t>
+        </is>
+      </c>
       <c r="P9" t="inlineStr">
         <is>
-          <t>Saxbergets östra sida,, Saxberget, Björnhyttan, Dlr</t>
+          <t>Saxberget, Dlr</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>499200</v>
+        <v>499146</v>
       </c>
       <c r="R9" t="n">
-        <v>6666216</v>
+        <v>6666307</v>
       </c>
       <c r="S9" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T9" t="inlineStr">
         <is>
@@ -1697,12 +1603,12 @@
       </c>
       <c r="Y9" t="inlineStr">
         <is>
-          <t>2024-07-29</t>
+          <t>2014-04-18</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
         <is>
-          <t>2024-07-29</t>
+          <t>2014-04-18</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1711,75 +1617,101 @@
       <c r="AE9" t="b">
         <v>0</v>
       </c>
-      <c r="AF9" t="inlineStr"/>
       <c r="AG9" t="b">
         <v>0</v>
+      </c>
+      <c r="AI9" t="inlineStr">
+        <is>
+          <t>lövrikt</t>
+        </is>
+      </c>
+      <c r="AJ9" t="inlineStr">
+        <is>
+          <t>asp</t>
+        </is>
+      </c>
+      <c r="AK9" t="inlineStr">
+        <is>
+          <t>Populus tremula</t>
+        </is>
+      </c>
+      <c r="AL9" t="inlineStr">
+        <is>
+          <t>klent träd</t>
+        </is>
+      </c>
+      <c r="AO9" t="inlineStr">
+        <is>
+          <t>Populus tremula # klent träd</t>
+        </is>
       </c>
       <c r="AT9" t="inlineStr"/>
       <c r="AW9" t="inlineStr">
         <is>
-          <t>Alec Bailey</t>
+          <t>Janolof Hermansson</t>
         </is>
       </c>
       <c r="AX9" t="inlineStr">
         <is>
-          <t>Alec Bailey</t>
+          <t>Janolof Hermansson</t>
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>118767476</v>
+        <v>7262080</v>
       </c>
       <c r="B10" t="n">
-        <v>90922</v>
-      </c>
-      <c r="C10" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80432</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>5321</v>
+        <v>6458</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Barkticka</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Rigidoporus corticola</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Fr.) Pouzar</t>
-        </is>
-      </c>
-      <c r="I10" t="inlineStr"/>
-      <c r="J10" t="inlineStr"/>
+          <t>(L.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr">
+        <is>
+          <t>16</t>
+        </is>
+      </c>
+      <c r="J10" t="inlineStr">
+        <is>
+          <t>cm²</t>
+        </is>
+      </c>
       <c r="K10" t="inlineStr"/>
-      <c r="N10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
-          <t>Saxbergets östra sida,, Saxberget, Björnhyttan, Dlr</t>
+          <t>Saxberget, Dlr</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>499200</v>
+        <v>499173</v>
       </c>
       <c r="R10" t="n">
-        <v>6666216</v>
+        <v>6666318</v>
       </c>
       <c r="S10" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T10" t="inlineStr">
         <is>
@@ -1803,12 +1735,17 @@
       </c>
       <c r="Y10" t="inlineStr">
         <is>
-          <t>2024-07-29</t>
+          <t>2014-04-18</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
         <is>
-          <t>2024-07-29</t>
+          <t>2014-04-18</t>
+        </is>
+      </c>
+      <c r="AC10" t="inlineStr">
+        <is>
+          <t>1 bål</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1817,22 +1754,1384 @@
       <c r="AE10" t="b">
         <v>0</v>
       </c>
-      <c r="AF10" t="inlineStr"/>
       <c r="AG10" t="b">
         <v>0</v>
+      </c>
+      <c r="AI10" t="inlineStr">
+        <is>
+          <t>granplantering</t>
+        </is>
+      </c>
+      <c r="AJ10" t="inlineStr">
+        <is>
+          <t>asp</t>
+        </is>
+      </c>
+      <c r="AK10" t="inlineStr">
+        <is>
+          <t>Populus tremula</t>
+        </is>
+      </c>
+      <c r="AL10" t="inlineStr">
+        <is>
+          <t>grovt träd</t>
+        </is>
+      </c>
+      <c r="AO10" t="inlineStr">
+        <is>
+          <t>Populus tremula # grovt träd</t>
+        </is>
       </c>
       <c r="AT10" t="inlineStr"/>
       <c r="AW10" t="inlineStr">
         <is>
+          <t>Janolof Hermansson</t>
+        </is>
+      </c>
+      <c r="AX10" t="inlineStr">
+        <is>
+          <t>Janolof Hermansson</t>
+        </is>
+      </c>
+      <c r="AY10" t="inlineStr"/>
+    </row>
+    <row r="11">
+      <c r="A11" t="n">
+        <v>95038065</v>
+      </c>
+      <c r="B11" t="n">
+        <v>80432</v>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E11" t="n">
+        <v>6458</v>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>Lunglav</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>Lobaria pulmonaria</t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>(L.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr"/>
+      <c r="J11" t="inlineStr"/>
+      <c r="K11" t="inlineStr"/>
+      <c r="N11" t="inlineStr"/>
+      <c r="P11" t="inlineStr">
+        <is>
+          <t>Saxberget, Dlr</t>
+        </is>
+      </c>
+      <c r="Q11" t="n">
+        <v>499156</v>
+      </c>
+      <c r="R11" t="n">
+        <v>6666243</v>
+      </c>
+      <c r="S11" t="n">
+        <v>25</v>
+      </c>
+      <c r="T11" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U11" t="inlineStr">
+        <is>
+          <t>Ludvika</t>
+        </is>
+      </c>
+      <c r="V11" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W11" t="inlineStr">
+        <is>
+          <t>Grangärde</t>
+        </is>
+      </c>
+      <c r="Y11" t="inlineStr">
+        <is>
+          <t>2021-06-23</t>
+        </is>
+      </c>
+      <c r="AA11" t="inlineStr">
+        <is>
+          <t>2021-06-23</t>
+        </is>
+      </c>
+      <c r="AC11" t="inlineStr">
+        <is>
+          <t>På två lövträd</t>
+        </is>
+      </c>
+      <c r="AD11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF11" t="inlineStr"/>
+      <c r="AG11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI11" t="inlineStr">
+        <is>
+          <t>Skogsmark</t>
+        </is>
+      </c>
+      <c r="AO11" t="inlineStr">
+        <is>
+          <t>På två lövträd</t>
+        </is>
+      </c>
+      <c r="AT11" t="inlineStr"/>
+      <c r="AW11" t="inlineStr">
+        <is>
+          <t>Henrik Larsson</t>
+        </is>
+      </c>
+      <c r="AX11" t="inlineStr">
+        <is>
+          <t>Henrik Larsson</t>
+        </is>
+      </c>
+      <c r="AY11" t="inlineStr"/>
+    </row>
+    <row r="12">
+      <c r="A12" t="n">
+        <v>95038071</v>
+      </c>
+      <c r="B12" t="n">
+        <v>80432</v>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E12" t="n">
+        <v>6458</v>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>Lunglav</t>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>Lobaria pulmonaria</t>
+        </is>
+      </c>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>(L.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr"/>
+      <c r="J12" t="inlineStr"/>
+      <c r="K12" t="inlineStr"/>
+      <c r="N12" t="inlineStr"/>
+      <c r="P12" t="inlineStr">
+        <is>
+          <t>Saxberget, Dlr</t>
+        </is>
+      </c>
+      <c r="Q12" t="n">
+        <v>499127</v>
+      </c>
+      <c r="R12" t="n">
+        <v>6666324</v>
+      </c>
+      <c r="S12" t="n">
+        <v>5</v>
+      </c>
+      <c r="T12" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U12" t="inlineStr">
+        <is>
+          <t>Ludvika</t>
+        </is>
+      </c>
+      <c r="V12" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W12" t="inlineStr">
+        <is>
+          <t>Grangärde</t>
+        </is>
+      </c>
+      <c r="Y12" t="inlineStr">
+        <is>
+          <t>2021-06-23</t>
+        </is>
+      </c>
+      <c r="AA12" t="inlineStr">
+        <is>
+          <t>2021-06-23</t>
+        </is>
+      </c>
+      <c r="AC12" t="inlineStr">
+        <is>
+          <t>Klen rönn</t>
+        </is>
+      </c>
+      <c r="AD12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF12" t="inlineStr"/>
+      <c r="AG12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI12" t="inlineStr">
+        <is>
+          <t>Skogsmark</t>
+        </is>
+      </c>
+      <c r="AO12" t="inlineStr">
+        <is>
+          <t>Klen rönn</t>
+        </is>
+      </c>
+      <c r="AT12" t="inlineStr"/>
+      <c r="AW12" t="inlineStr">
+        <is>
+          <t>Henrik Larsson</t>
+        </is>
+      </c>
+      <c r="AX12" t="inlineStr">
+        <is>
+          <t>Henrik Larsson</t>
+        </is>
+      </c>
+      <c r="AY12" t="inlineStr"/>
+    </row>
+    <row r="13">
+      <c r="A13" t="n">
+        <v>95682788</v>
+      </c>
+      <c r="B13" t="n">
+        <v>80432</v>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E13" t="n">
+        <v>6458</v>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>Lunglav</t>
+        </is>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>Lobaria pulmonaria</t>
+        </is>
+      </c>
+      <c r="H13" t="inlineStr">
+        <is>
+          <t>(L.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr"/>
+      <c r="J13" t="inlineStr"/>
+      <c r="K13" t="inlineStr"/>
+      <c r="N13" t="inlineStr"/>
+      <c r="P13" t="inlineStr">
+        <is>
+          <t>Saxberget, Dlr</t>
+        </is>
+      </c>
+      <c r="Q13" t="n">
+        <v>499091</v>
+      </c>
+      <c r="R13" t="n">
+        <v>6666280</v>
+      </c>
+      <c r="S13" t="n">
+        <v>5</v>
+      </c>
+      <c r="T13" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U13" t="inlineStr">
+        <is>
+          <t>Ludvika</t>
+        </is>
+      </c>
+      <c r="V13" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W13" t="inlineStr">
+        <is>
+          <t>Grangärde</t>
+        </is>
+      </c>
+      <c r="Y13" t="inlineStr">
+        <is>
+          <t>2021-06-23</t>
+        </is>
+      </c>
+      <c r="AA13" t="inlineStr">
+        <is>
+          <t>2021-06-23</t>
+        </is>
+      </c>
+      <c r="AD13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF13" t="inlineStr"/>
+      <c r="AG13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI13" t="inlineStr">
+        <is>
+          <t>skogsmark</t>
+        </is>
+      </c>
+      <c r="AJ13" t="inlineStr">
+        <is>
+          <t>vanlig rönn</t>
+        </is>
+      </c>
+      <c r="AK13" t="inlineStr">
+        <is>
+          <t>Sorbus aucuparia subsp. aucuparia</t>
+        </is>
+      </c>
+      <c r="AO13" t="inlineStr">
+        <is>
+          <t>Sorbus aucuparia subsp. aucuparia</t>
+        </is>
+      </c>
+      <c r="AT13" t="inlineStr"/>
+      <c r="AW13" t="inlineStr">
+        <is>
+          <t>Henrik Larsson</t>
+        </is>
+      </c>
+      <c r="AX13" t="inlineStr">
+        <is>
+          <t>Henrik Larsson</t>
+        </is>
+      </c>
+      <c r="AY13" t="inlineStr"/>
+    </row>
+    <row r="14">
+      <c r="A14" t="n">
+        <v>95682797</v>
+      </c>
+      <c r="B14" t="n">
+        <v>80432</v>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E14" t="n">
+        <v>6458</v>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>Lunglav</t>
+        </is>
+      </c>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>Lobaria pulmonaria</t>
+        </is>
+      </c>
+      <c r="H14" t="inlineStr">
+        <is>
+          <t>(L.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr"/>
+      <c r="J14" t="inlineStr"/>
+      <c r="K14" t="inlineStr"/>
+      <c r="N14" t="inlineStr"/>
+      <c r="P14" t="inlineStr">
+        <is>
+          <t>Saxberget, Dlr</t>
+        </is>
+      </c>
+      <c r="Q14" t="n">
+        <v>499092</v>
+      </c>
+      <c r="R14" t="n">
+        <v>6666288</v>
+      </c>
+      <c r="S14" t="n">
+        <v>5</v>
+      </c>
+      <c r="T14" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U14" t="inlineStr">
+        <is>
+          <t>Ludvika</t>
+        </is>
+      </c>
+      <c r="V14" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W14" t="inlineStr">
+        <is>
+          <t>Grangärde</t>
+        </is>
+      </c>
+      <c r="Y14" t="inlineStr">
+        <is>
+          <t>2021-06-23</t>
+        </is>
+      </c>
+      <c r="AA14" t="inlineStr">
+        <is>
+          <t>2021-06-23</t>
+        </is>
+      </c>
+      <c r="AD14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF14" t="inlineStr"/>
+      <c r="AG14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI14" t="inlineStr">
+        <is>
+          <t>Skogsmark</t>
+        </is>
+      </c>
+      <c r="AJ14" t="inlineStr">
+        <is>
+          <t>vanlig rönn</t>
+        </is>
+      </c>
+      <c r="AK14" t="inlineStr">
+        <is>
+          <t>Sorbus aucuparia subsp. aucuparia</t>
+        </is>
+      </c>
+      <c r="AL14" t="inlineStr">
+        <is>
+          <t>rönn</t>
+        </is>
+      </c>
+      <c r="AO14" t="inlineStr">
+        <is>
+          <t>Sorbus aucuparia subsp. aucuparia # rönn</t>
+        </is>
+      </c>
+      <c r="AT14" t="inlineStr"/>
+      <c r="AW14" t="inlineStr">
+        <is>
+          <t>Henrik Larsson</t>
+        </is>
+      </c>
+      <c r="AX14" t="inlineStr">
+        <is>
+          <t>Henrik Larsson</t>
+        </is>
+      </c>
+      <c r="AY14" t="inlineStr"/>
+    </row>
+    <row r="15">
+      <c r="A15" t="n">
+        <v>118767473</v>
+      </c>
+      <c r="B15" t="n">
+        <v>80432</v>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E15" t="n">
+        <v>6458</v>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>Lunglav</t>
+        </is>
+      </c>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>Lobaria pulmonaria</t>
+        </is>
+      </c>
+      <c r="H15" t="inlineStr">
+        <is>
+          <t>(L.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr"/>
+      <c r="J15" t="inlineStr"/>
+      <c r="K15" t="inlineStr"/>
+      <c r="N15" t="inlineStr"/>
+      <c r="P15" t="inlineStr">
+        <is>
+          <t>Saxbergets östra sida,, Saxberget, Björnhyttan, Dlr</t>
+        </is>
+      </c>
+      <c r="Q15" t="n">
+        <v>499200</v>
+      </c>
+      <c r="R15" t="n">
+        <v>6666216</v>
+      </c>
+      <c r="S15" t="n">
+        <v>10</v>
+      </c>
+      <c r="T15" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U15" t="inlineStr">
+        <is>
+          <t>Ludvika</t>
+        </is>
+      </c>
+      <c r="V15" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W15" t="inlineStr">
+        <is>
+          <t>Grangärde</t>
+        </is>
+      </c>
+      <c r="Y15" t="inlineStr">
+        <is>
+          <t>2024-07-29</t>
+        </is>
+      </c>
+      <c r="AA15" t="inlineStr">
+        <is>
+          <t>2024-07-29</t>
+        </is>
+      </c>
+      <c r="AD15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF15" t="inlineStr"/>
+      <c r="AG15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT15" t="inlineStr"/>
+      <c r="AW15" t="inlineStr">
+        <is>
           <t>Alec Bailey</t>
         </is>
       </c>
-      <c r="AX10" t="inlineStr">
+      <c r="AX15" t="inlineStr">
         <is>
           <t>Alec Bailey</t>
         </is>
       </c>
-      <c r="AY10" t="inlineStr"/>
+      <c r="AY15" t="inlineStr"/>
+    </row>
+    <row r="16">
+      <c r="A16" t="n">
+        <v>7262077</v>
+      </c>
+      <c r="B16" t="n">
+        <v>80467</v>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E16" t="n">
+        <v>6463</v>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>Bårdlav</t>
+        </is>
+      </c>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>Nephroma parile</t>
+        </is>
+      </c>
+      <c r="H16" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr"/>
+      <c r="J16" t="inlineStr"/>
+      <c r="K16" t="inlineStr"/>
+      <c r="P16" t="inlineStr">
+        <is>
+          <t>Saxberget, Dlr</t>
+        </is>
+      </c>
+      <c r="Q16" t="n">
+        <v>499124</v>
+      </c>
+      <c r="R16" t="n">
+        <v>6666324</v>
+      </c>
+      <c r="S16" t="n">
+        <v>5</v>
+      </c>
+      <c r="T16" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U16" t="inlineStr">
+        <is>
+          <t>Ludvika</t>
+        </is>
+      </c>
+      <c r="V16" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W16" t="inlineStr">
+        <is>
+          <t>Grangärde</t>
+        </is>
+      </c>
+      <c r="Y16" t="inlineStr">
+        <is>
+          <t>2014-04-18</t>
+        </is>
+      </c>
+      <c r="AA16" t="inlineStr">
+        <is>
+          <t>2014-04-18</t>
+        </is>
+      </c>
+      <c r="AD16" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE16" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG16" t="b">
+        <v>0</v>
+      </c>
+      <c r="AH16" t="inlineStr">
+        <is>
+          <t>Barrskog i branter</t>
+        </is>
+      </c>
+      <c r="AI16" t="inlineStr">
+        <is>
+          <t>lövrikt</t>
+        </is>
+      </c>
+      <c r="AJ16" t="inlineStr">
+        <is>
+          <t>rönn</t>
+        </is>
+      </c>
+      <c r="AK16" t="inlineStr">
+        <is>
+          <t>Sorbus aucuparia</t>
+        </is>
+      </c>
+      <c r="AL16" t="inlineStr">
+        <is>
+          <t>gammalt klent träd</t>
+        </is>
+      </c>
+      <c r="AM16" t="inlineStr">
+        <is>
+          <t>Bark på levande träd</t>
+        </is>
+      </c>
+      <c r="AO16" t="inlineStr">
+        <is>
+          <t>Bark on living woody plant # Sorbus aucuparia # gammalt klent träd</t>
+        </is>
+      </c>
+      <c r="AT16" t="inlineStr"/>
+      <c r="AW16" t="inlineStr">
+        <is>
+          <t>Janolof Hermansson</t>
+        </is>
+      </c>
+      <c r="AX16" t="inlineStr">
+        <is>
+          <t>Janolof Hermansson</t>
+        </is>
+      </c>
+      <c r="AY16" t="inlineStr"/>
+    </row>
+    <row r="17">
+      <c r="A17" t="n">
+        <v>103879479</v>
+      </c>
+      <c r="B17" t="n">
+        <v>5004</v>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E17" t="n">
+        <v>105212</v>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>Barrpraktbagge</t>
+        </is>
+      </c>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>Chrysobothris chrysostigma</t>
+        </is>
+      </c>
+      <c r="H17" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="J17" t="inlineStr"/>
+      <c r="K17" t="inlineStr"/>
+      <c r="L17" t="inlineStr"/>
+      <c r="M17" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
+      <c r="N17" t="inlineStr"/>
+      <c r="P17" t="inlineStr">
+        <is>
+          <t>Saxdals leden, Saxberget, Björnhyttan, Dlr</t>
+        </is>
+      </c>
+      <c r="Q17" t="n">
+        <v>499025</v>
+      </c>
+      <c r="R17" t="n">
+        <v>6665919</v>
+      </c>
+      <c r="S17" t="n">
+        <v>25</v>
+      </c>
+      <c r="T17" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U17" t="inlineStr">
+        <is>
+          <t>Ludvika</t>
+        </is>
+      </c>
+      <c r="V17" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W17" t="inlineStr">
+        <is>
+          <t>Grangärde</t>
+        </is>
+      </c>
+      <c r="Y17" t="inlineStr">
+        <is>
+          <t>2022-10-02</t>
+        </is>
+      </c>
+      <c r="AA17" t="inlineStr">
+        <is>
+          <t>2022-10-02</t>
+        </is>
+      </c>
+      <c r="AC17" t="inlineStr">
+        <is>
+          <t>Gnagspåren kan vara mellan 2 och 5 år gamla</t>
+        </is>
+      </c>
+      <c r="AD17" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE17" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF17" t="inlineStr"/>
+      <c r="AG17" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT17" t="inlineStr"/>
+      <c r="AW17" t="inlineStr">
+        <is>
+          <t>Alec Bailey</t>
+        </is>
+      </c>
+      <c r="AX17" t="inlineStr">
+        <is>
+          <t>Alec Bailey</t>
+        </is>
+      </c>
+      <c r="AY17" t="inlineStr"/>
+    </row>
+    <row r="18">
+      <c r="A18" t="n">
+        <v>95038138</v>
+      </c>
+      <c r="B18" t="n">
+        <v>56905</v>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E18" t="n">
+        <v>208260</v>
+      </c>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>Huggorm</t>
+        </is>
+      </c>
+      <c r="G18" t="inlineStr">
+        <is>
+          <t>Vipera berus</t>
+        </is>
+      </c>
+      <c r="H18" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J18" t="inlineStr">
+        <is>
+          <t>ex.</t>
+        </is>
+      </c>
+      <c r="K18" t="inlineStr"/>
+      <c r="L18" t="inlineStr"/>
+      <c r="M18" t="inlineStr">
+        <is>
+          <t>vilande</t>
+        </is>
+      </c>
+      <c r="N18" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
+      <c r="P18" t="inlineStr">
+        <is>
+          <t>Saxberget, Dlr</t>
+        </is>
+      </c>
+      <c r="Q18" t="n">
+        <v>499271</v>
+      </c>
+      <c r="R18" t="n">
+        <v>6666032</v>
+      </c>
+      <c r="S18" t="n">
+        <v>5</v>
+      </c>
+      <c r="T18" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U18" t="inlineStr">
+        <is>
+          <t>Ludvika</t>
+        </is>
+      </c>
+      <c r="V18" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W18" t="inlineStr">
+        <is>
+          <t>Grangärde</t>
+        </is>
+      </c>
+      <c r="Y18" t="inlineStr">
+        <is>
+          <t>2021-06-29</t>
+        </is>
+      </c>
+      <c r="AA18" t="inlineStr">
+        <is>
+          <t>2021-06-29</t>
+        </is>
+      </c>
+      <c r="AC18" t="inlineStr">
+        <is>
+          <t>Vilande på stig</t>
+        </is>
+      </c>
+      <c r="AD18" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE18" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF18" t="inlineStr"/>
+      <c r="AG18" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI18" t="inlineStr">
+        <is>
+          <t>Skogsmark</t>
+        </is>
+      </c>
+      <c r="AT18" t="inlineStr"/>
+      <c r="AW18" t="inlineStr">
+        <is>
+          <t>Henrik Larsson</t>
+        </is>
+      </c>
+      <c r="AX18" t="inlineStr">
+        <is>
+          <t>Henrik Larsson</t>
+        </is>
+      </c>
+      <c r="AY18" t="inlineStr"/>
+    </row>
+    <row r="19">
+      <c r="A19" t="n">
+        <v>7262071</v>
+      </c>
+      <c r="B19" t="n">
+        <v>101326</v>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E19" t="n">
+        <v>222498</v>
+      </c>
+      <c r="F19" t="inlineStr">
+        <is>
+          <t>Blåsippa</t>
+        </is>
+      </c>
+      <c r="G19" t="inlineStr">
+        <is>
+          <t>Hepatica nobilis</t>
+        </is>
+      </c>
+      <c r="H19" t="inlineStr">
+        <is>
+          <t>Schreb.</t>
+        </is>
+      </c>
+      <c r="I19" t="inlineStr"/>
+      <c r="J19" t="inlineStr"/>
+      <c r="K19" t="inlineStr"/>
+      <c r="L19" t="inlineStr"/>
+      <c r="P19" t="inlineStr">
+        <is>
+          <t>Saxberget, Dlr</t>
+        </is>
+      </c>
+      <c r="Q19" t="n">
+        <v>499163</v>
+      </c>
+      <c r="R19" t="n">
+        <v>6666234</v>
+      </c>
+      <c r="S19" t="n">
+        <v>5</v>
+      </c>
+      <c r="T19" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U19" t="inlineStr">
+        <is>
+          <t>Ludvika</t>
+        </is>
+      </c>
+      <c r="V19" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W19" t="inlineStr">
+        <is>
+          <t>Grangärde</t>
+        </is>
+      </c>
+      <c r="Y19" t="inlineStr">
+        <is>
+          <t>2014-04-18</t>
+        </is>
+      </c>
+      <c r="AA19" t="inlineStr">
+        <is>
+          <t>2014-04-18</t>
+        </is>
+      </c>
+      <c r="AD19" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE19" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG19" t="b">
+        <v>0</v>
+      </c>
+      <c r="AH19" t="inlineStr">
+        <is>
+          <t>Barrskog i branter</t>
+        </is>
+      </c>
+      <c r="AI19" t="inlineStr">
+        <is>
+          <t>lövrikt</t>
+        </is>
+      </c>
+      <c r="AT19" t="inlineStr"/>
+      <c r="AW19" t="inlineStr">
+        <is>
+          <t>Janolof Hermansson</t>
+        </is>
+      </c>
+      <c r="AX19" t="inlineStr">
+        <is>
+          <t>Janolof Hermansson</t>
+        </is>
+      </c>
+      <c r="AY19" t="inlineStr"/>
+    </row>
+    <row r="20">
+      <c r="A20" t="n">
+        <v>7262073</v>
+      </c>
+      <c r="B20" t="n">
+        <v>80392</v>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E20" t="n">
+        <v>229497</v>
+      </c>
+      <c r="F20" t="inlineStr">
+        <is>
+          <t>Korallblylav</t>
+        </is>
+      </c>
+      <c r="G20" t="inlineStr">
+        <is>
+          <t>Parmeliella triptophylla</t>
+        </is>
+      </c>
+      <c r="H20" t="inlineStr">
+        <is>
+          <t>(Ach.) Müll.Arg.</t>
+        </is>
+      </c>
+      <c r="I20" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="J20" t="inlineStr">
+        <is>
+          <t>dm²</t>
+        </is>
+      </c>
+      <c r="K20" t="inlineStr"/>
+      <c r="P20" t="inlineStr">
+        <is>
+          <t>Saxberget, Dlr</t>
+        </is>
+      </c>
+      <c r="Q20" t="n">
+        <v>499105</v>
+      </c>
+      <c r="R20" t="n">
+        <v>6666292</v>
+      </c>
+      <c r="S20" t="n">
+        <v>5</v>
+      </c>
+      <c r="T20" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U20" t="inlineStr">
+        <is>
+          <t>Ludvika</t>
+        </is>
+      </c>
+      <c r="V20" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W20" t="inlineStr">
+        <is>
+          <t>Grangärde</t>
+        </is>
+      </c>
+      <c r="Y20" t="inlineStr">
+        <is>
+          <t>2014-04-18</t>
+        </is>
+      </c>
+      <c r="AA20" t="inlineStr">
+        <is>
+          <t>2014-04-18</t>
+        </is>
+      </c>
+      <c r="AD20" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE20" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG20" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI20" t="inlineStr">
+        <is>
+          <t>lövrikt</t>
+        </is>
+      </c>
+      <c r="AJ20" t="inlineStr">
+        <is>
+          <t>asp</t>
+        </is>
+      </c>
+      <c r="AK20" t="inlineStr">
+        <is>
+          <t>Populus tremula</t>
+        </is>
+      </c>
+      <c r="AL20" t="inlineStr">
+        <is>
+          <t>gammalt träd</t>
+        </is>
+      </c>
+      <c r="AM20" t="inlineStr">
+        <is>
+          <t>Bark på levande träd</t>
+        </is>
+      </c>
+      <c r="AO20" t="inlineStr">
+        <is>
+          <t>Bark on living woody plant # Populus tremula # gammalt träd</t>
+        </is>
+      </c>
+      <c r="AT20" t="inlineStr"/>
+      <c r="AW20" t="inlineStr">
+        <is>
+          <t>Janolof Hermansson</t>
+        </is>
+      </c>
+      <c r="AX20" t="inlineStr">
+        <is>
+          <t>Janolof Hermansson</t>
+        </is>
+      </c>
+      <c r="AY20" t="inlineStr"/>
+    </row>
+    <row r="21">
+      <c r="A21" t="n">
+        <v>7262081</v>
+      </c>
+      <c r="B21" t="n">
+        <v>80392</v>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E21" t="n">
+        <v>229497</v>
+      </c>
+      <c r="F21" t="inlineStr">
+        <is>
+          <t>Korallblylav</t>
+        </is>
+      </c>
+      <c r="G21" t="inlineStr">
+        <is>
+          <t>Parmeliella triptophylla</t>
+        </is>
+      </c>
+      <c r="H21" t="inlineStr">
+        <is>
+          <t>(Ach.) Müll.Arg.</t>
+        </is>
+      </c>
+      <c r="I21" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J21" t="inlineStr">
+        <is>
+          <t>m²</t>
+        </is>
+      </c>
+      <c r="K21" t="inlineStr"/>
+      <c r="P21" t="inlineStr">
+        <is>
+          <t>Saxberget, Dlr</t>
+        </is>
+      </c>
+      <c r="Q21" t="n">
+        <v>499173</v>
+      </c>
+      <c r="R21" t="n">
+        <v>6666318</v>
+      </c>
+      <c r="S21" t="n">
+        <v>5</v>
+      </c>
+      <c r="T21" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U21" t="inlineStr">
+        <is>
+          <t>Ludvika</t>
+        </is>
+      </c>
+      <c r="V21" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W21" t="inlineStr">
+        <is>
+          <t>Grangärde</t>
+        </is>
+      </c>
+      <c r="Y21" t="inlineStr">
+        <is>
+          <t>2014-04-18</t>
+        </is>
+      </c>
+      <c r="AA21" t="inlineStr">
+        <is>
+          <t>2014-04-18</t>
+        </is>
+      </c>
+      <c r="AD21" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE21" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG21" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI21" t="inlineStr">
+        <is>
+          <t>granplantering</t>
+        </is>
+      </c>
+      <c r="AJ21" t="inlineStr">
+        <is>
+          <t>asp</t>
+        </is>
+      </c>
+      <c r="AK21" t="inlineStr">
+        <is>
+          <t>Populus tremula</t>
+        </is>
+      </c>
+      <c r="AL21" t="inlineStr">
+        <is>
+          <t>grovt träd</t>
+        </is>
+      </c>
+      <c r="AO21" t="inlineStr">
+        <is>
+          <t>Populus tremula # grovt träd</t>
+        </is>
+      </c>
+      <c r="AT21" t="inlineStr"/>
+      <c r="AW21" t="inlineStr">
+        <is>
+          <t>Janolof Hermansson</t>
+        </is>
+      </c>
+      <c r="AX21" t="inlineStr">
+        <is>
+          <t>Janolof Hermansson</t>
+        </is>
+      </c>
+      <c r="AY21" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
